--- a/XAUUSD_News_Analysis.xlsx
+++ b/XAUUSD_News_Analysis.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O1663"/>
+  <dimension ref="A1:O1669"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -98464,6 +98464,360 @@
         <v>0.8036799511375786</v>
       </c>
     </row>
+    <row r="1664">
+      <c r="A1664" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B1664" t="inlineStr">
+        <is>
+          <t>Retail Sales m/m</t>
+        </is>
+      </c>
+      <c r="C1664" t="inlineStr">
+        <is>
+          <t>15:30</t>
+        </is>
+      </c>
+      <c r="D1664" t="b">
+        <v>0</v>
+      </c>
+      <c r="E1664" t="inlineStr">
+        <is>
+          <t>BULLISH</t>
+        </is>
+      </c>
+      <c r="F1664" t="n">
+        <v>31.76</v>
+      </c>
+      <c r="G1664" t="inlineStr">
+        <is>
+          <t>BEARISH</t>
+        </is>
+      </c>
+      <c r="H1664" t="n">
+        <v>4.52</v>
+      </c>
+      <c r="I1664" t="inlineStr">
+        <is>
+          <t>BULLISH</t>
+        </is>
+      </c>
+      <c r="J1664" t="n">
+        <v>11.28</v>
+      </c>
+      <c r="K1664" t="b">
+        <v>0</v>
+      </c>
+      <c r="L1664" t="n">
+        <v>89.1228571428569</v>
+      </c>
+      <c r="M1664" t="n">
+        <v>0.3563620042958366</v>
+      </c>
+      <c r="N1664" t="n">
+        <v>0.05071650690860142</v>
+      </c>
+      <c r="O1664" t="n">
+        <v>0.1265668579488991</v>
+      </c>
+    </row>
+    <row r="1665">
+      <c r="A1665" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B1665" t="inlineStr">
+        <is>
+          <t>Core Retail Sales m/m</t>
+        </is>
+      </c>
+      <c r="C1665" t="inlineStr">
+        <is>
+          <t>15:30</t>
+        </is>
+      </c>
+      <c r="D1665" t="b">
+        <v>0</v>
+      </c>
+      <c r="E1665" t="inlineStr">
+        <is>
+          <t>BULLISH</t>
+        </is>
+      </c>
+      <c r="F1665" t="n">
+        <v>31.76</v>
+      </c>
+      <c r="G1665" t="inlineStr">
+        <is>
+          <t>BEARISH</t>
+        </is>
+      </c>
+      <c r="H1665" t="n">
+        <v>4.52</v>
+      </c>
+      <c r="I1665" t="inlineStr">
+        <is>
+          <t>BULLISH</t>
+        </is>
+      </c>
+      <c r="J1665" t="n">
+        <v>11.28</v>
+      </c>
+      <c r="K1665" t="b">
+        <v>0</v>
+      </c>
+      <c r="L1665" t="n">
+        <v>89.1228571428569</v>
+      </c>
+      <c r="M1665" t="n">
+        <v>0.3563620042958366</v>
+      </c>
+      <c r="N1665" t="n">
+        <v>0.05071650690860142</v>
+      </c>
+      <c r="O1665" t="n">
+        <v>0.1265668579488991</v>
+      </c>
+    </row>
+    <row r="1666">
+      <c r="A1666" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B1666" t="inlineStr">
+        <is>
+          <t>EIA Crude Oil Stocks Change</t>
+        </is>
+      </c>
+      <c r="C1666" t="inlineStr">
+        <is>
+          <t>17:30</t>
+        </is>
+      </c>
+      <c r="D1666" t="b">
+        <v>0</v>
+      </c>
+      <c r="E1666" t="inlineStr">
+        <is>
+          <t>BULLISH</t>
+        </is>
+      </c>
+      <c r="F1666" t="n">
+        <v>37.58</v>
+      </c>
+      <c r="G1666" t="inlineStr">
+        <is>
+          <t>BULLISH</t>
+        </is>
+      </c>
+      <c r="H1666" t="n">
+        <v>7.22</v>
+      </c>
+      <c r="I1666" t="inlineStr">
+        <is>
+          <t>BULLISH</t>
+        </is>
+      </c>
+      <c r="J1666" t="n">
+        <v>16.05</v>
+      </c>
+      <c r="K1666" t="b">
+        <v>0</v>
+      </c>
+      <c r="L1666" t="n">
+        <v>89.1228571428569</v>
+      </c>
+      <c r="M1666" t="n">
+        <v>0.421665117173726</v>
+      </c>
+      <c r="N1666" t="n">
+        <v>0.08101176546019961</v>
+      </c>
+      <c r="O1666" t="n">
+        <v>0.180088481390056</v>
+      </c>
+    </row>
+    <row r="1667">
+      <c r="A1667" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B1667" t="inlineStr">
+        <is>
+          <t>Fed Interest Rate Decision</t>
+        </is>
+      </c>
+      <c r="C1667" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="D1667" t="b">
+        <v>0</v>
+      </c>
+      <c r="E1667" t="inlineStr">
+        <is>
+          <t>BEARISH</t>
+        </is>
+      </c>
+      <c r="F1667" t="n">
+        <v>20.1</v>
+      </c>
+      <c r="G1667" t="inlineStr">
+        <is>
+          <t>BULLISH</t>
+        </is>
+      </c>
+      <c r="H1667" t="n">
+        <v>23.14</v>
+      </c>
+      <c r="I1667" t="inlineStr">
+        <is>
+          <t>BEARISH</t>
+        </is>
+      </c>
+      <c r="J1667" t="n">
+        <v>61.82</v>
+      </c>
+      <c r="K1667" t="b">
+        <v>0</v>
+      </c>
+      <c r="L1667" t="n">
+        <v>89.1228571428569</v>
+      </c>
+      <c r="M1667" t="n">
+        <v>0.2255313692174533</v>
+      </c>
+      <c r="N1667" t="n">
+        <v>0.2596415862533268</v>
+      </c>
+      <c r="O1667" t="n">
+        <v>0.6936492161702965</v>
+      </c>
+    </row>
+    <row r="1668">
+      <c r="A1668" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B1668" t="inlineStr">
+        <is>
+          <t>Initial Jobless Claims</t>
+        </is>
+      </c>
+      <c r="C1668" t="inlineStr">
+        <is>
+          <t>15:30</t>
+        </is>
+      </c>
+      <c r="D1668" t="b">
+        <v>0</v>
+      </c>
+      <c r="E1668" t="inlineStr">
+        <is>
+          <t>BULLISH</t>
+        </is>
+      </c>
+      <c r="F1668" t="n">
+        <v>70.20999999999999</v>
+      </c>
+      <c r="G1668" t="inlineStr">
+        <is>
+          <t>BULLISH</t>
+        </is>
+      </c>
+      <c r="H1668" t="n">
+        <v>17.95</v>
+      </c>
+      <c r="I1668" t="inlineStr">
+        <is>
+          <t>BEARISH</t>
+        </is>
+      </c>
+      <c r="J1668" t="n">
+        <v>20.97</v>
+      </c>
+      <c r="K1668" t="b">
+        <v>0</v>
+      </c>
+      <c r="L1668" t="n">
+        <v>89.88142857142832</v>
+      </c>
+      <c r="M1668" t="n">
+        <v>0.7811402323696319</v>
+      </c>
+      <c r="N1668" t="n">
+        <v>0.1997075512182722</v>
+      </c>
+      <c r="O1668" t="n">
+        <v>0.2333073732059704</v>
+      </c>
+    </row>
+    <row r="1669">
+      <c r="A1669" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B1669" t="inlineStr">
+        <is>
+          <t>Philadelphia Fed Manufacturing Index</t>
+        </is>
+      </c>
+      <c r="C1669" t="inlineStr">
+        <is>
+          <t>15:30</t>
+        </is>
+      </c>
+      <c r="D1669" t="b">
+        <v>0</v>
+      </c>
+      <c r="E1669" t="inlineStr">
+        <is>
+          <t>BULLISH</t>
+        </is>
+      </c>
+      <c r="F1669" t="n">
+        <v>70.20999999999999</v>
+      </c>
+      <c r="G1669" t="inlineStr">
+        <is>
+          <t>BULLISH</t>
+        </is>
+      </c>
+      <c r="H1669" t="n">
+        <v>17.95</v>
+      </c>
+      <c r="I1669" t="inlineStr">
+        <is>
+          <t>BEARISH</t>
+        </is>
+      </c>
+      <c r="J1669" t="n">
+        <v>20.97</v>
+      </c>
+      <c r="K1669" t="b">
+        <v>0</v>
+      </c>
+      <c r="L1669" t="n">
+        <v>89.88142857142832</v>
+      </c>
+      <c r="M1669" t="n">
+        <v>0.7811402323696319</v>
+      </c>
+      <c r="N1669" t="n">
+        <v>0.1997075512182722</v>
+      </c>
+      <c r="O1669" t="n">
+        <v>0.2333073732059704</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/XAUUSD_News_Analysis.xlsx
+++ b/XAUUSD_News_Analysis.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O1669"/>
+  <dimension ref="A1:O1673"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -98818,6 +98818,242 @@
         <v>0.2333073732059704</v>
       </c>
     </row>
+    <row r="1670">
+      <c r="A1670" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B1670" t="inlineStr">
+        <is>
+          <t>EIA Crude Oil Stocks Change</t>
+        </is>
+      </c>
+      <c r="C1670" t="inlineStr">
+        <is>
+          <t>17:30</t>
+        </is>
+      </c>
+      <c r="D1670" t="b">
+        <v>0</v>
+      </c>
+      <c r="E1670" t="inlineStr">
+        <is>
+          <t>BEARISH</t>
+        </is>
+      </c>
+      <c r="F1670" t="n">
+        <v>44.33</v>
+      </c>
+      <c r="G1670" t="inlineStr">
+        <is>
+          <t>BULLISH</t>
+        </is>
+      </c>
+      <c r="H1670" t="n">
+        <v>7.14</v>
+      </c>
+      <c r="I1670" t="inlineStr">
+        <is>
+          <t>BULLISH</t>
+        </is>
+      </c>
+      <c r="J1670" t="n">
+        <v>11.01</v>
+      </c>
+      <c r="K1670" t="b">
+        <v>0</v>
+      </c>
+      <c r="L1670" t="n">
+        <v>78.39571428571415</v>
+      </c>
+      <c r="M1670" t="n">
+        <v>0.5654645844342813</v>
+      </c>
+      <c r="N1670" t="n">
+        <v>0.09107640723800514</v>
+      </c>
+      <c r="O1670" t="n">
+        <v>0.1404413506569239</v>
+      </c>
+    </row>
+    <row r="1671">
+      <c r="A1671" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="B1671" t="inlineStr">
+        <is>
+          <t>Initial Jobless Claims</t>
+        </is>
+      </c>
+      <c r="C1671" t="inlineStr">
+        <is>
+          <t>15:30</t>
+        </is>
+      </c>
+      <c r="D1671" t="b">
+        <v>0</v>
+      </c>
+      <c r="E1671" t="inlineStr">
+        <is>
+          <t>BEARISH</t>
+        </is>
+      </c>
+      <c r="F1671" t="n">
+        <v>43.72</v>
+      </c>
+      <c r="G1671" t="inlineStr">
+        <is>
+          <t>BULLISH</t>
+        </is>
+      </c>
+      <c r="H1671" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="I1671" t="inlineStr">
+        <is>
+          <t>BULLISH</t>
+        </is>
+      </c>
+      <c r="J1671" t="n">
+        <v>9.699999999999999</v>
+      </c>
+      <c r="K1671" t="b">
+        <v>0</v>
+      </c>
+      <c r="L1671" t="n">
+        <v>81.21857142857132</v>
+      </c>
+      <c r="M1671" t="n">
+        <v>0.5383005294355626</v>
+      </c>
+      <c r="N1671" t="n">
+        <v>0.06279352013086388</v>
+      </c>
+      <c r="O1671" t="n">
+        <v>0.1194308127979176</v>
+      </c>
+    </row>
+    <row r="1672">
+      <c r="A1672" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="B1672" t="inlineStr">
+        <is>
+          <t>New Home Sales</t>
+        </is>
+      </c>
+      <c r="C1672" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="D1672" t="b">
+        <v>1</v>
+      </c>
+      <c r="E1672" t="inlineStr">
+        <is>
+          <t>BEARISH</t>
+        </is>
+      </c>
+      <c r="F1672" t="n">
+        <v>18.74</v>
+      </c>
+      <c r="G1672" t="inlineStr">
+        <is>
+          <t>BEARISH</t>
+        </is>
+      </c>
+      <c r="H1672" t="n">
+        <v>7.3</v>
+      </c>
+      <c r="I1672" t="inlineStr">
+        <is>
+          <t>BEARISH</t>
+        </is>
+      </c>
+      <c r="J1672" t="n">
+        <v>9.25</v>
+      </c>
+      <c r="K1672" t="b">
+        <v>1</v>
+      </c>
+      <c r="L1672" t="n">
+        <v>81.21857142857132</v>
+      </c>
+      <c r="M1672" t="n">
+        <v>0.2307354053436057</v>
+      </c>
+      <c r="N1672" t="n">
+        <v>0.0898809209716287</v>
+      </c>
+      <c r="O1672" t="n">
+        <v>0.1138902080804884</v>
+      </c>
+    </row>
+    <row r="1673">
+      <c r="A1673" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="B1673" t="inlineStr">
+        <is>
+          <t>Durable Goods Orders m/m</t>
+        </is>
+      </c>
+      <c r="C1673" t="inlineStr">
+        <is>
+          <t>15:30</t>
+        </is>
+      </c>
+      <c r="D1673" t="b">
+        <v>0</v>
+      </c>
+      <c r="E1673" t="inlineStr">
+        <is>
+          <t>BULLISH</t>
+        </is>
+      </c>
+      <c r="F1673" t="n">
+        <v>49.37</v>
+      </c>
+      <c r="G1673" t="inlineStr">
+        <is>
+          <t>BULLISH</t>
+        </is>
+      </c>
+      <c r="H1673" t="n">
+        <v>11.76</v>
+      </c>
+      <c r="I1673" t="inlineStr">
+        <is>
+          <t>BEARISH</t>
+        </is>
+      </c>
+      <c r="J1673" t="n">
+        <v>11.73</v>
+      </c>
+      <c r="K1673" t="b">
+        <v>0</v>
+      </c>
+      <c r="L1673" t="n">
+        <v>81.2892857142856</v>
+      </c>
+      <c r="M1673" t="n">
+        <v>0.6073371117261992</v>
+      </c>
+      <c r="N1673" t="n">
+        <v>0.1446685119282986</v>
+      </c>
+      <c r="O1673" t="n">
+        <v>0.1442994596019509</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/XAUUSD_News_Analysis.xlsx
+++ b/XAUUSD_News_Analysis.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O1673"/>
+  <dimension ref="A1:O1689"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -99054,6 +99054,950 @@
         <v>0.1442994596019509</v>
       </c>
     </row>
+    <row r="1674">
+      <c r="A1674" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="B1674" t="inlineStr">
+        <is>
+          <t>JOLTS Job Openings</t>
+        </is>
+      </c>
+      <c r="C1674" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="D1674" t="b">
+        <v>0</v>
+      </c>
+      <c r="E1674" t="inlineStr">
+        <is>
+          <t>BULLISH</t>
+        </is>
+      </c>
+      <c r="F1674" t="n">
+        <v>26.82</v>
+      </c>
+      <c r="G1674" t="inlineStr">
+        <is>
+          <t>BEARISH</t>
+        </is>
+      </c>
+      <c r="H1674" t="n">
+        <v>7.51</v>
+      </c>
+      <c r="I1674" t="inlineStr">
+        <is>
+          <t>BULLISH</t>
+        </is>
+      </c>
+      <c r="J1674" t="n">
+        <v>14.42</v>
+      </c>
+      <c r="K1674" t="b">
+        <v>0</v>
+      </c>
+      <c r="L1674" t="n">
+        <v>77.30214285714275</v>
+      </c>
+      <c r="M1674" t="n">
+        <v>0.3469502785914274</v>
+      </c>
+      <c r="N1674" t="n">
+        <v>0.09715125250639894</v>
+      </c>
+      <c r="O1674" t="n">
+        <v>0.1865407538138845</v>
+      </c>
+    </row>
+    <row r="1675">
+      <c r="A1675" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="B1675" t="inlineStr">
+        <is>
+          <t>CB Consumer Confidence Index</t>
+        </is>
+      </c>
+      <c r="C1675" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="D1675" t="b">
+        <v>0</v>
+      </c>
+      <c r="E1675" t="inlineStr">
+        <is>
+          <t>BULLISH</t>
+        </is>
+      </c>
+      <c r="F1675" t="n">
+        <v>26.82</v>
+      </c>
+      <c r="G1675" t="inlineStr">
+        <is>
+          <t>BEARISH</t>
+        </is>
+      </c>
+      <c r="H1675" t="n">
+        <v>7.51</v>
+      </c>
+      <c r="I1675" t="inlineStr">
+        <is>
+          <t>BULLISH</t>
+        </is>
+      </c>
+      <c r="J1675" t="n">
+        <v>14.42</v>
+      </c>
+      <c r="K1675" t="b">
+        <v>0</v>
+      </c>
+      <c r="L1675" t="n">
+        <v>77.30214285714275</v>
+      </c>
+      <c r="M1675" t="n">
+        <v>0.3469502785914274</v>
+      </c>
+      <c r="N1675" t="n">
+        <v>0.09715125250639894</v>
+      </c>
+      <c r="O1675" t="n">
+        <v>0.1865407538138845</v>
+      </c>
+    </row>
+    <row r="1676">
+      <c r="A1676" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="B1676" t="inlineStr">
+        <is>
+          <t>ADP Nonfarm Employment Change</t>
+        </is>
+      </c>
+      <c r="C1676" t="inlineStr">
+        <is>
+          <t>15:15</t>
+        </is>
+      </c>
+      <c r="D1676" t="b">
+        <v>0</v>
+      </c>
+      <c r="E1676" t="inlineStr">
+        <is>
+          <t>BULLISH</t>
+        </is>
+      </c>
+      <c r="F1676" t="n">
+        <v>28.5</v>
+      </c>
+      <c r="G1676" t="inlineStr">
+        <is>
+          <t>BULLISH</t>
+        </is>
+      </c>
+      <c r="H1676" t="n">
+        <v>9.76</v>
+      </c>
+      <c r="I1676" t="inlineStr">
+        <is>
+          <t>BULLISH</t>
+        </is>
+      </c>
+      <c r="J1676" t="n">
+        <v>35.6</v>
+      </c>
+      <c r="K1676" t="b">
+        <v>0</v>
+      </c>
+      <c r="L1676" t="n">
+        <v>79.7257142857142</v>
+      </c>
+      <c r="M1676" t="n">
+        <v>0.3574756307339453</v>
+      </c>
+      <c r="N1676" t="n">
+        <v>0.1224197247706423</v>
+      </c>
+      <c r="O1676" t="n">
+        <v>0.4465309633027528</v>
+      </c>
+    </row>
+    <row r="1677">
+      <c r="A1677" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="B1677" t="inlineStr">
+        <is>
+          <t>GDP q/q</t>
+        </is>
+      </c>
+      <c r="C1677" t="inlineStr">
+        <is>
+          <t>15:30</t>
+        </is>
+      </c>
+      <c r="D1677" t="b">
+        <v>0</v>
+      </c>
+      <c r="E1677" t="inlineStr">
+        <is>
+          <t>BULLISH</t>
+        </is>
+      </c>
+      <c r="F1677" t="n">
+        <v>26.51</v>
+      </c>
+      <c r="G1677" t="inlineStr">
+        <is>
+          <t>BULLISH</t>
+        </is>
+      </c>
+      <c r="H1677" t="n">
+        <v>10.08</v>
+      </c>
+      <c r="I1677" t="inlineStr">
+        <is>
+          <t>BULLISH</t>
+        </is>
+      </c>
+      <c r="J1677" t="n">
+        <v>26.93</v>
+      </c>
+      <c r="K1677" t="b">
+        <v>0</v>
+      </c>
+      <c r="L1677" t="n">
+        <v>79.7257142857142</v>
+      </c>
+      <c r="M1677" t="n">
+        <v>0.3325150516055049</v>
+      </c>
+      <c r="N1677" t="n">
+        <v>0.1264334862385322</v>
+      </c>
+      <c r="O1677" t="n">
+        <v>0.3377831135321104</v>
+      </c>
+    </row>
+    <row r="1678">
+      <c r="A1678" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="B1678" t="inlineStr">
+        <is>
+          <t>GDP Sales q/q</t>
+        </is>
+      </c>
+      <c r="C1678" t="inlineStr">
+        <is>
+          <t>15:30</t>
+        </is>
+      </c>
+      <c r="D1678" t="b">
+        <v>0</v>
+      </c>
+      <c r="E1678" t="inlineStr">
+        <is>
+          <t>BULLISH</t>
+        </is>
+      </c>
+      <c r="F1678" t="n">
+        <v>26.51</v>
+      </c>
+      <c r="G1678" t="inlineStr">
+        <is>
+          <t>BULLISH</t>
+        </is>
+      </c>
+      <c r="H1678" t="n">
+        <v>10.08</v>
+      </c>
+      <c r="I1678" t="inlineStr">
+        <is>
+          <t>BULLISH</t>
+        </is>
+      </c>
+      <c r="J1678" t="n">
+        <v>26.93</v>
+      </c>
+      <c r="K1678" t="b">
+        <v>0</v>
+      </c>
+      <c r="L1678" t="n">
+        <v>79.7257142857142</v>
+      </c>
+      <c r="M1678" t="n">
+        <v>0.3325150516055049</v>
+      </c>
+      <c r="N1678" t="n">
+        <v>0.1264334862385322</v>
+      </c>
+      <c r="O1678" t="n">
+        <v>0.3377831135321104</v>
+      </c>
+    </row>
+    <row r="1679">
+      <c r="A1679" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="B1679" t="inlineStr">
+        <is>
+          <t>Core PCE Price Index m/m</t>
+        </is>
+      </c>
+      <c r="C1679" t="inlineStr">
+        <is>
+          <t>15:30</t>
+        </is>
+      </c>
+      <c r="D1679" t="b">
+        <v>0</v>
+      </c>
+      <c r="E1679" t="inlineStr">
+        <is>
+          <t>BULLISH</t>
+        </is>
+      </c>
+      <c r="F1679" t="n">
+        <v>26.51</v>
+      </c>
+      <c r="G1679" t="inlineStr">
+        <is>
+          <t>BULLISH</t>
+        </is>
+      </c>
+      <c r="H1679" t="n">
+        <v>10.08</v>
+      </c>
+      <c r="I1679" t="inlineStr">
+        <is>
+          <t>BULLISH</t>
+        </is>
+      </c>
+      <c r="J1679" t="n">
+        <v>26.93</v>
+      </c>
+      <c r="K1679" t="b">
+        <v>0</v>
+      </c>
+      <c r="L1679" t="n">
+        <v>79.7257142857142</v>
+      </c>
+      <c r="M1679" t="n">
+        <v>0.3325150516055049</v>
+      </c>
+      <c r="N1679" t="n">
+        <v>0.1264334862385322</v>
+      </c>
+      <c r="O1679" t="n">
+        <v>0.3377831135321104</v>
+      </c>
+    </row>
+    <row r="1680">
+      <c r="A1680" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="B1680" t="inlineStr">
+        <is>
+          <t>Core PCE Price Index y/y</t>
+        </is>
+      </c>
+      <c r="C1680" t="inlineStr">
+        <is>
+          <t>15:30</t>
+        </is>
+      </c>
+      <c r="D1680" t="b">
+        <v>0</v>
+      </c>
+      <c r="E1680" t="inlineStr">
+        <is>
+          <t>BULLISH</t>
+        </is>
+      </c>
+      <c r="F1680" t="n">
+        <v>26.51</v>
+      </c>
+      <c r="G1680" t="inlineStr">
+        <is>
+          <t>BULLISH</t>
+        </is>
+      </c>
+      <c r="H1680" t="n">
+        <v>10.08</v>
+      </c>
+      <c r="I1680" t="inlineStr">
+        <is>
+          <t>BULLISH</t>
+        </is>
+      </c>
+      <c r="J1680" t="n">
+        <v>26.93</v>
+      </c>
+      <c r="K1680" t="b">
+        <v>0</v>
+      </c>
+      <c r="L1680" t="n">
+        <v>79.7257142857142</v>
+      </c>
+      <c r="M1680" t="n">
+        <v>0.3325150516055049</v>
+      </c>
+      <c r="N1680" t="n">
+        <v>0.1264334862385322</v>
+      </c>
+      <c r="O1680" t="n">
+        <v>0.3377831135321104</v>
+      </c>
+    </row>
+    <row r="1681">
+      <c r="A1681" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="B1681" t="inlineStr">
+        <is>
+          <t>MNI Chicago Business Barometer</t>
+        </is>
+      </c>
+      <c r="C1681" t="inlineStr">
+        <is>
+          <t>16:45</t>
+        </is>
+      </c>
+      <c r="D1681" t="b">
+        <v>0</v>
+      </c>
+      <c r="E1681" t="inlineStr">
+        <is>
+          <t>BEARISH</t>
+        </is>
+      </c>
+      <c r="F1681" t="n">
+        <v>42.66</v>
+      </c>
+      <c r="G1681" t="inlineStr">
+        <is>
+          <t>BEARISH</t>
+        </is>
+      </c>
+      <c r="H1681" t="n">
+        <v>12.18</v>
+      </c>
+      <c r="I1681" t="inlineStr">
+        <is>
+          <t>BEARISH</t>
+        </is>
+      </c>
+      <c r="J1681" t="n">
+        <v>10.89</v>
+      </c>
+      <c r="K1681" t="b">
+        <v>0</v>
+      </c>
+      <c r="L1681" t="n">
+        <v>79.7257142857142</v>
+      </c>
+      <c r="M1681" t="n">
+        <v>0.5350845756880739</v>
+      </c>
+      <c r="N1681" t="n">
+        <v>0.1527737958715598</v>
+      </c>
+      <c r="O1681" t="n">
+        <v>0.1365933199541286</v>
+      </c>
+    </row>
+    <row r="1682">
+      <c r="A1682" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="B1682" t="inlineStr">
+        <is>
+          <t>EIA Crude Oil Stocks Change</t>
+        </is>
+      </c>
+      <c r="C1682" t="inlineStr">
+        <is>
+          <t>17:30</t>
+        </is>
+      </c>
+      <c r="D1682" t="b">
+        <v>0</v>
+      </c>
+      <c r="E1682" t="inlineStr">
+        <is>
+          <t>BEARISH</t>
+        </is>
+      </c>
+      <c r="F1682" t="n">
+        <v>46.7</v>
+      </c>
+      <c r="G1682" t="inlineStr">
+        <is>
+          <t>BEARISH</t>
+        </is>
+      </c>
+      <c r="H1682" t="n">
+        <v>10.35</v>
+      </c>
+      <c r="I1682" t="inlineStr">
+        <is>
+          <t>BULLISH</t>
+        </is>
+      </c>
+      <c r="J1682" t="n">
+        <v>10.43</v>
+      </c>
+      <c r="K1682" t="b">
+        <v>0</v>
+      </c>
+      <c r="L1682" t="n">
+        <v>79.7257142857142</v>
+      </c>
+      <c r="M1682" t="n">
+        <v>0.5857583142201841</v>
+      </c>
+      <c r="N1682" t="n">
+        <v>0.1298200974770644</v>
+      </c>
+      <c r="O1682" t="n">
+        <v>0.1308235378440368</v>
+      </c>
+    </row>
+    <row r="1683">
+      <c r="A1683" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="B1683" t="inlineStr">
+        <is>
+          <t>Initial Jobless Claims</t>
+        </is>
+      </c>
+      <c r="C1683" t="inlineStr">
+        <is>
+          <t>15:30</t>
+        </is>
+      </c>
+      <c r="D1683" t="b">
+        <v>0</v>
+      </c>
+      <c r="E1683" t="inlineStr">
+        <is>
+          <t>BEARISH</t>
+        </is>
+      </c>
+      <c r="F1683" t="n">
+        <v>43.39</v>
+      </c>
+      <c r="G1683" t="inlineStr">
+        <is>
+          <t>BULLISH</t>
+        </is>
+      </c>
+      <c r="H1683" t="n">
+        <v>5.31</v>
+      </c>
+      <c r="I1683" t="inlineStr">
+        <is>
+          <t>BULLISH</t>
+        </is>
+      </c>
+      <c r="J1683" t="n">
+        <v>9.75</v>
+      </c>
+      <c r="K1683" t="b">
+        <v>0</v>
+      </c>
+      <c r="L1683" t="n">
+        <v>77.95999999999997</v>
+      </c>
+      <c r="M1683" t="n">
+        <v>0.5565674704976914</v>
+      </c>
+      <c r="N1683" t="n">
+        <v>0.06811185223191382</v>
+      </c>
+      <c r="O1683" t="n">
+        <v>0.1250641354540791</v>
+      </c>
+    </row>
+    <row r="1684">
+      <c r="A1684" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="B1684" t="inlineStr">
+        <is>
+          <t>S&amp;P Global Manufacturing PMI</t>
+        </is>
+      </c>
+      <c r="C1684" t="inlineStr">
+        <is>
+          <t>16:45</t>
+        </is>
+      </c>
+      <c r="D1684" t="b">
+        <v>0</v>
+      </c>
+      <c r="E1684" t="inlineStr">
+        <is>
+          <t>BEARISH</t>
+        </is>
+      </c>
+      <c r="F1684" t="n">
+        <v>38.91</v>
+      </c>
+      <c r="G1684" t="inlineStr">
+        <is>
+          <t>BEARISH</t>
+        </is>
+      </c>
+      <c r="H1684" t="n">
+        <v>9.27</v>
+      </c>
+      <c r="I1684" t="inlineStr">
+        <is>
+          <t>BEARISH</t>
+        </is>
+      </c>
+      <c r="J1684" t="n">
+        <v>12.12</v>
+      </c>
+      <c r="K1684" t="b">
+        <v>0</v>
+      </c>
+      <c r="L1684" t="n">
+        <v>77.95999999999997</v>
+      </c>
+      <c r="M1684" t="n">
+        <v>0.499102103642894</v>
+      </c>
+      <c r="N1684" t="n">
+        <v>0.1189071318624936</v>
+      </c>
+      <c r="O1684" t="n">
+        <v>0.1554643406875321</v>
+      </c>
+    </row>
+    <row r="1685">
+      <c r="A1685" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="B1685" t="inlineStr">
+        <is>
+          <t>ISM Manufacturing PMI</t>
+        </is>
+      </c>
+      <c r="C1685" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="D1685" t="b">
+        <v>1</v>
+      </c>
+      <c r="E1685" t="inlineStr">
+        <is>
+          <t>BEARISH</t>
+        </is>
+      </c>
+      <c r="F1685" t="n">
+        <v>26.12</v>
+      </c>
+      <c r="G1685" t="inlineStr">
+        <is>
+          <t>BULLISH</t>
+        </is>
+      </c>
+      <c r="H1685" t="n">
+        <v>5.26</v>
+      </c>
+      <c r="I1685" t="inlineStr">
+        <is>
+          <t>BEARISH</t>
+        </is>
+      </c>
+      <c r="J1685" t="n">
+        <v>14.97</v>
+      </c>
+      <c r="K1685" t="b">
+        <v>1</v>
+      </c>
+      <c r="L1685" t="n">
+        <v>77.95999999999997</v>
+      </c>
+      <c r="M1685" t="n">
+        <v>0.3350436121087739</v>
+      </c>
+      <c r="N1685" t="n">
+        <v>0.06747049769112368</v>
+      </c>
+      <c r="O1685" t="n">
+        <v>0.1920215495125706</v>
+      </c>
+    </row>
+    <row r="1686">
+      <c r="A1686" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="B1686" t="inlineStr">
+        <is>
+          <t>ISM Manufacturing Prices Paid</t>
+        </is>
+      </c>
+      <c r="C1686" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="D1686" t="b">
+        <v>1</v>
+      </c>
+      <c r="E1686" t="inlineStr">
+        <is>
+          <t>BEARISH</t>
+        </is>
+      </c>
+      <c r="F1686" t="n">
+        <v>26.12</v>
+      </c>
+      <c r="G1686" t="inlineStr">
+        <is>
+          <t>BULLISH</t>
+        </is>
+      </c>
+      <c r="H1686" t="n">
+        <v>5.26</v>
+      </c>
+      <c r="I1686" t="inlineStr">
+        <is>
+          <t>BEARISH</t>
+        </is>
+      </c>
+      <c r="J1686" t="n">
+        <v>14.97</v>
+      </c>
+      <c r="K1686" t="b">
+        <v>1</v>
+      </c>
+      <c r="L1686" t="n">
+        <v>77.95999999999997</v>
+      </c>
+      <c r="M1686" t="n">
+        <v>0.3350436121087739</v>
+      </c>
+      <c r="N1686" t="n">
+        <v>0.06747049769112368</v>
+      </c>
+      <c r="O1686" t="n">
+        <v>0.1920215495125706</v>
+      </c>
+    </row>
+    <row r="1687">
+      <c r="A1687" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="B1687" t="inlineStr">
+        <is>
+          <t>Unemployment Rate</t>
+        </is>
+      </c>
+      <c r="C1687" t="inlineStr">
+        <is>
+          <t>15:30</t>
+        </is>
+      </c>
+      <c r="D1687" t="b">
+        <v>0</v>
+      </c>
+      <c r="E1687" t="inlineStr">
+        <is>
+          <t>BEARISH</t>
+        </is>
+      </c>
+      <c r="F1687" t="n">
+        <v>30.39</v>
+      </c>
+      <c r="G1687" t="inlineStr">
+        <is>
+          <t>BULLISH</t>
+        </is>
+      </c>
+      <c r="H1687" t="n">
+        <v>10.62</v>
+      </c>
+      <c r="I1687" t="inlineStr">
+        <is>
+          <t>BULLISH</t>
+        </is>
+      </c>
+      <c r="J1687" t="n">
+        <v>41.51</v>
+      </c>
+      <c r="K1687" t="b">
+        <v>0</v>
+      </c>
+      <c r="L1687" t="n">
+        <v>77.77499999999996</v>
+      </c>
+      <c r="M1687" t="n">
+        <v>0.3907425265188044</v>
+      </c>
+      <c r="N1687" t="n">
+        <v>0.1365477338476375</v>
+      </c>
+      <c r="O1687" t="n">
+        <v>0.5337190613950501</v>
+      </c>
+    </row>
+    <row r="1688">
+      <c r="A1688" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="B1688" t="inlineStr">
+        <is>
+          <t>Nonfarm Payrolls</t>
+        </is>
+      </c>
+      <c r="C1688" t="inlineStr">
+        <is>
+          <t>15:30</t>
+        </is>
+      </c>
+      <c r="D1688" t="b">
+        <v>0</v>
+      </c>
+      <c r="E1688" t="inlineStr">
+        <is>
+          <t>BEARISH</t>
+        </is>
+      </c>
+      <c r="F1688" t="n">
+        <v>30.39</v>
+      </c>
+      <c r="G1688" t="inlineStr">
+        <is>
+          <t>BULLISH</t>
+        </is>
+      </c>
+      <c r="H1688" t="n">
+        <v>10.62</v>
+      </c>
+      <c r="I1688" t="inlineStr">
+        <is>
+          <t>BULLISH</t>
+        </is>
+      </c>
+      <c r="J1688" t="n">
+        <v>41.51</v>
+      </c>
+      <c r="K1688" t="b">
+        <v>0</v>
+      </c>
+      <c r="L1688" t="n">
+        <v>77.77499999999996</v>
+      </c>
+      <c r="M1688" t="n">
+        <v>0.3907425265188044</v>
+      </c>
+      <c r="N1688" t="n">
+        <v>0.1365477338476375</v>
+      </c>
+      <c r="O1688" t="n">
+        <v>0.5337190613950501</v>
+      </c>
+    </row>
+    <row r="1689">
+      <c r="A1689" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="B1689" t="inlineStr">
+        <is>
+          <t>Average Hourly Earnings m/m</t>
+        </is>
+      </c>
+      <c r="C1689" t="inlineStr">
+        <is>
+          <t>15:30</t>
+        </is>
+      </c>
+      <c r="D1689" t="b">
+        <v>0</v>
+      </c>
+      <c r="E1689" t="inlineStr">
+        <is>
+          <t>BEARISH</t>
+        </is>
+      </c>
+      <c r="F1689" t="n">
+        <v>30.39</v>
+      </c>
+      <c r="G1689" t="inlineStr">
+        <is>
+          <t>BULLISH</t>
+        </is>
+      </c>
+      <c r="H1689" t="n">
+        <v>10.62</v>
+      </c>
+      <c r="I1689" t="inlineStr">
+        <is>
+          <t>BULLISH</t>
+        </is>
+      </c>
+      <c r="J1689" t="n">
+        <v>41.51</v>
+      </c>
+      <c r="K1689" t="b">
+        <v>0</v>
+      </c>
+      <c r="L1689" t="n">
+        <v>77.77499999999996</v>
+      </c>
+      <c r="M1689" t="n">
+        <v>0.3907425265188044</v>
+      </c>
+      <c r="N1689" t="n">
+        <v>0.1365477338476375</v>
+      </c>
+      <c r="O1689" t="n">
+        <v>0.5337190613950501</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
